--- a/Evaluación-fase-1/Registro_Interesados_Bomberos.xlsx
+++ b/Evaluación-fase-1/Registro_Interesados_Bomberos.xlsx
@@ -94,7 +94,7 @@
     <t>Stakeholder principal / supervision operativa</t>
   </si>
   <si>
-    <t>Informacion consolidada, trazabilidad y control de inventarios, unidades, mantenimiento y reportes.</t>
+    <t>Informacion consolidada de inventarios, unidades, check in, mantenimiento y reportes, distinguir stock propio de Comandancia y entregas a companias con salida y recepcion trazables.</t>
   </si>
   <si>
     <t>Analisis / Diseño / Validacion / Uso</t>
@@ -124,19 +124,19 @@
     <t>STK-02</t>
   </si>
   <si>
-    <t>Superintendencia / administracion institucional</t>
-  </si>
-  <si>
-    <t>Representante institucional</t>
+    <t>Superintendencia / administracion de Bomberos</t>
+  </si>
+  <si>
+    <t>Representante de Bomberos</t>
   </si>
   <si>
     <t>Superintendencia / administracion</t>
   </si>
   <si>
-    <t>Gestion institucional y toma de decisiones</t>
-  </si>
-  <si>
-    <t>Visibilidad del uso y estado de los recursos y apoyo para decisiones institucionales.</t>
+    <t>Gestion de Bomberos y toma de decisiones</t>
+  </si>
+  <si>
+    <t>Visibilidad del uso y estado de los recursos y apoyo para decisiones de Bomberos.</t>
   </si>
   <si>
     <t>Hitos / Validacion / Cierre</t>
@@ -175,7 +175,7 @@
     <t>Usuarios organizacionales principales</t>
   </si>
   <si>
-    <t>Gestionar inventario, unidades y movimientos propios sin mezclar informacion con otras compañias.</t>
+    <t>Gestionar inventario, unidades y movimientos propios, el maquinista registra el check in diario y el capitan supervisa cumplimiento y historial de su compania. Permisos concretos por validar.</t>
   </si>
   <si>
     <t>Analisis / Desarrollo / Validacion / Uso</t>
@@ -196,7 +196,7 @@
     <t>Usuarios operativos de inventario</t>
   </si>
   <si>
-    <t>Registrar y consultar articulos, cantidades, series, estados, ubicaciones, altas, bajas y perdidas con trazabilidad.</t>
+    <t>Registrar articulos, cantidades, series, estados, ubicaciones, bajas y perdidas, contemplar al inspector de Material Menor y entregas de Comandancia con recepcion vinculada, segun permisos por validar.</t>
   </si>
   <si>
     <t>Mantener informado</t>
@@ -217,7 +217,7 @@
     <t>Usuarios operativos de unidades y mantenimiento</t>
   </si>
   <si>
-    <t>Controlar unidades, kilometraje, horas, revisiones, mantenimiento preventivo/correctivo y alertas.</t>
+    <t>Controlar unidades, kilometraje, horas y alertas, el inspector documenta mantenimiento, pruebas y fotos anteriores y posteriores. Distinguir conformidad del capitan de cierre tecnico, pendiente de definir.</t>
   </si>
   <si>
     <t>STK-06</t>
@@ -256,10 +256,10 @@
     <t>Tecnologia / infraestructura</t>
   </si>
   <si>
-    <t>Soporte tecnico e infraestructura</t>
-  </si>
-  <si>
-    <t>Disponer de una solucion instalable en servidor local, accesible por red interna, respaldable y recuperable.</t>
+    <t>Soporte tecnico y infraestructura</t>
+  </si>
+  <si>
+    <t>Validar servidor, red interna y acceso remoto seguro desde computadores, telefonos y tablets, capacidad para fotos historicas, respaldo y recuperacion. Infraestructura, sesiones y responsables por confirmar.</t>
   </si>
   <si>
     <t>Diseño tecnico / Implementacion / Operacion</t>
@@ -406,7 +406,7 @@
     <t>Obtiene mayor visibilidad sobre recursos, estados y necesidades de reposicion o mantenimiento.</t>
   </si>
   <si>
-    <t>Mejor apoyo a decisiones institucionales y control de recursos.</t>
+    <t>Mejor apoyo a decisiones de Bomberos y control de recursos.</t>
   </si>
   <si>
     <t>Requiere informacion resumida y consistente para no aumentar carga administrativa.</t>
@@ -526,7 +526,7 @@
     <t>Involucrar en decisiones clave, validacion de prioridades y revisiones del Incremento.</t>
   </si>
   <si>
-    <t>STK-02 Superintendencia / administracion institucional</t>
+    <t>STK-02 Superintendencia / administracion de Bomberos</t>
   </si>
   <si>
     <t>Mantener visibilidad ejecutiva y solicitar validacion en hitos relevantes.</t>
@@ -586,7 +586,7 @@
     <t>STK-11 Bomberos de san bernardo / organismos de control</t>
   </si>
   <si>
-    <t>Mantener disponibilidad de informacion institucional cuando sea requerida.</t>
+    <t>Mantener disponibilidad de informacion de Bomberos cuando sea requerida.</t>
   </si>
   <si>
     <t>Simbolo</t>
@@ -640,10 +640,10 @@
     <t>Semanal / por Sprint</t>
   </si>
   <si>
-    <t>Entregar resumenes ejecutivos, hitos relevantes, riesgos y decisiones que afecten recursos o alcance institucional.</t>
-  </si>
-  <si>
-    <t>Mantener apoyo institucional sin sobrecargar con detalle tecnico.</t>
+    <t>Entregar resumenes ejecutivos, hitos relevantes, riesgos y decisiones que afecten recursos o alcance de Bomberos.</t>
+  </si>
+  <si>
+    <t>Mantener apoyo de Bomberos sin sobrecargar con detalle tecnico.</t>
   </si>
   <si>
     <t>Por hito</t>
@@ -658,7 +658,7 @@
     <t>Por Sprint</t>
   </si>
   <si>
-    <t>Revisar pantallas de inventario, series, estados, ubicaciones, altas y bajas; solicitar feedback funcional.</t>
+    <t>Revisar pantallas de inventario, series, estados, ubicaciones, altas y bajas, solicitar feedback funcional.</t>
   </si>
   <si>
     <t>Asegurar que el modulo refleje la operacion diaria de inventario.</t>
@@ -757,7 +757,7 @@
     <t>Canal</t>
   </si>
   <si>
-    <t>Avance funcional, decisiones, riesgos, historias proximas y resultados de validacion.</t>
+    <t>Avance, decisiones y riesgos, validar supervision consolidada del check in, stock propio de Comandancia y entregas a companias.</t>
   </si>
   <si>
     <t>Reunion breve, demostracion, tablero Jira o resumen ejecutivo.</t>
@@ -772,13 +772,13 @@
     <t>Reunion / Jira / correo</t>
   </si>
   <si>
-    <t>Hitos, estado general, riesgos y decisiones institucionales relevantes.</t>
+    <t>Hitos, estado general, riesgos y decisiones relevantes de Bomberos.</t>
   </si>
   <si>
     <t>Resumen ejecutivo y reunion de hito.</t>
   </si>
   <si>
-    <t>Informacion / decision institucional</t>
+    <t>Informacion / decision de Bomberos</t>
   </si>
   <si>
     <t>Mantener apoyo y confianza en el proyecto.</t>
@@ -787,7 +787,7 @@
     <t>Informe / reunion</t>
   </si>
   <si>
-    <t>Cambios funcionales, demostraciones, procesos de inventario, unidades y permisos.</t>
+    <t>Demostraciones de inventario y permisos, check in del maquinista, supervision y historial propio del capitan y conformidad de recepcion por precisar.</t>
   </si>
   <si>
     <t>Demostracion y resumen operativo.</t>
@@ -802,7 +802,7 @@
     <t>Demo / reunion</t>
   </si>
   <si>
-    <t>Inventario, series, estados, ubicaciones, altas, bajas y trazabilidad.</t>
+    <t>Inventario, series, estados, ubicaciones y bajas, validar registro de entregas desde Comandancia y recepcion vinculada con Material Menor.</t>
   </si>
   <si>
     <t>Pantallas, prototipos y pruebas funcionales.</t>
@@ -817,7 +817,7 @@
     <t>Figma / demo / reunion</t>
   </si>
   <si>
-    <t>Unidades, kilometraje, horas, check in, mantenimiento, historial y alertas.</t>
+    <t>Unidades, lecturas, alertas y mantenimiento, observaciones del inspector, trabajos, pruebas y fotos historicas, conformidad del capitan y cierre por precisar.</t>
   </si>
   <si>
     <t>Prototipos, reportes tecnicos y demostraciones.</t>
@@ -847,7 +847,7 @@
     <t>Canal interno de compañia</t>
   </si>
   <si>
-    <t>Arquitectura, servidor, red, base de datos, respaldo, seguridad y despliegue.</t>
+    <t>Arquitectura, red, servidor y despliegue, validar acceso remoto seguro, sesiones en tablets, capacidad fotografica y recuperacion de datos y adjuntos.</t>
   </si>
   <si>
     <t>Documento tecnico, diagramas y reunion tecnica.</t>
@@ -940,7 +940,7 @@
     <t>Alta capacidad de decision y uso directo de informacion consolidada.</t>
   </si>
   <si>
-    <t>Tiene autoridad institucional, pero no requiere detalle operativo permanente.</t>
+    <t>Tiene autoridad en Bomberos, pero no requiere detalle operativo permanente.</t>
   </si>
   <si>
     <t>Son usuarios organizacionales principales y su adopcion afecta el exito del producto.</t>
@@ -967,7 +967,7 @@
     <t>Su relacion es puntual y externa al uso diario del sistema.</t>
   </si>
   <si>
-    <t>Puede requerir informacion institucional y tiene influencia en control o auditoria.</t>
+    <t>Puede requerir informacion de Bomberos y tiene influencia en control o auditoria.</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1060,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1082,8 +1082,14 @@
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1485,7 +1491,7 @@
       <c r="F4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -1506,7 +1512,7 @@
       <c r="M4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>28</v>
       </c>
       <c r="O4" s="4" t="s">
@@ -1520,55 +1526,55 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="Q5" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1591,7 +1597,7 @@
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>50</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -1612,7 +1618,7 @@
       <c r="M6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="7" t="s">
         <v>28</v>
       </c>
       <c r="O6" s="4" t="s">
@@ -1626,55 +1632,55 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="10" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1697,7 +1703,7 @@
       <c r="F8" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>64</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -1718,7 +1724,7 @@
       <c r="M8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="7" t="s">
         <v>28</v>
       </c>
       <c r="O8" s="4" t="s">
@@ -1732,55 +1738,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="N9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="10" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1800,10 +1806,10 @@
       <c r="E10" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>78</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -1824,7 +1830,7 @@
       <c r="M10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="7" t="s">
         <v>41</v>
       </c>
       <c r="O10" s="4" t="s">
@@ -1838,55 +1844,55 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="N11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="P11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="10" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1930,7 +1936,7 @@
       <c r="M12" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="7" t="s">
         <v>98</v>
       </c>
       <c r="O12" s="4" t="s">
@@ -1944,55 +1950,55 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="P13" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="Q13" s="8" t="s">
+      <c r="Q13" s="10" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2000,7 +2006,7 @@
       <c r="A14" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -2036,7 +2042,7 @@
       <c r="M14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="7" t="s">
         <v>98</v>
       </c>
       <c r="O14" s="4" t="s">
@@ -4010,19 +4016,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="10" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4044,19 +4050,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4078,19 +4084,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="10" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4112,19 +4118,19 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="10" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4146,19 +4152,19 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="10" t="s">
         <v>152</v>
       </c>
     </row>
@@ -4166,7 +4172,7 @@
       <c r="A14" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -4462,7 +4468,7 @@
       </c>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -4519,25 +4525,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="10" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4565,25 +4571,25 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="10" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4611,25 +4617,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="8"/>
+      <c r="G10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="10" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4657,23 +4663,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="10" t="s">
         <v>181</v>
       </c>
     </row>
@@ -4699,28 +4705,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="10" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>186</v>
       </c>
       <c r="B15" s="4"/>
@@ -4736,71 +4742,71 @@
       <c r="H15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="19" ht="40.5" customHeight="1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="13" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="20" ht="40.5" customHeight="1">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="15" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="21" ht="40.5" customHeight="1">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="15" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="22" ht="40.5" customHeight="1">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="15" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="15" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="24" ht="40.5" customHeight="1">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="15" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="25" ht="40.5" customHeight="1">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="15" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="15" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4890,25 +4896,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="10" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4936,25 +4942,25 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="10" t="s">
         <v>213</v>
       </c>
     </row>
@@ -4982,25 +4988,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="10" t="s">
         <v>219</v>
       </c>
     </row>
@@ -5028,25 +5034,25 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="10" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5074,25 +5080,25 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="10" t="s">
         <v>231</v>
       </c>
     </row>
@@ -5100,7 +5106,7 @@
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -5187,7 +5193,7 @@
       <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>244</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -5210,31 +5216,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="10" t="s">
         <v>253</v>
       </c>
     </row>
@@ -5245,7 +5251,7 @@
       <c r="B6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>254</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -5268,31 +5274,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="10" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5303,7 +5309,7 @@
       <c r="B8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>264</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -5326,31 +5332,31 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="10" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5361,7 +5367,7 @@
       <c r="B10" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>274</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -5384,31 +5390,31 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="10" t="s">
         <v>285</v>
       </c>
     </row>
@@ -5442,31 +5448,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="10" t="s">
         <v>295</v>
       </c>
     </row>
@@ -5474,7 +5480,7 @@
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -5574,22 +5580,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>305</v>
       </c>
     </row>
@@ -5614,22 +5620,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>307</v>
       </c>
     </row>
@@ -5654,22 +5660,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="10" t="s">
         <v>309</v>
       </c>
     </row>
@@ -5694,10 +5700,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -5706,10 +5712,10 @@
       <c r="D11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>311</v>
       </c>
     </row>
@@ -5734,22 +5740,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>313</v>
       </c>
     </row>
@@ -5757,19 +5763,19 @@
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>314</v>
       </c>
     </row>
